--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{21708DCC-3D40-4B1F-8156-44C48D6B6461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50FA514-63EF-49AF-B78C-52E7252F7C6E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF96A9E-FB1A-4F82-90CC-0F46C2486A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="77">
   <si>
     <t>No</t>
   </si>
@@ -146,9 +146,6 @@
     <t>https://uk.rs-online.com/web/p/clip-kits/1440700</t>
   </si>
   <si>
-    <t>336-821</t>
-  </si>
-  <si>
     <t>Tubing</t>
   </si>
   <si>
@@ -176,15 +173,6 @@
     <t>OLED screen</t>
   </si>
   <si>
-    <t>1.3 inch yellow oled screen</t>
-  </si>
-  <si>
-    <t>254-3587</t>
-  </si>
-  <si>
-    <t>MDOB128064XV-YI | Midas 1.28 in Passive matrix Yellow OLED Display 128 x 64 pixel COB I2C | RS</t>
-  </si>
-  <si>
     <t>SD card reader</t>
   </si>
   <si>
@@ -225,6 +213,60 @@
   </si>
   <si>
     <t>5 way lever connector for smaller wires</t>
+  </si>
+  <si>
+    <t>Pneumatic fitting</t>
+  </si>
+  <si>
+    <t>121-6039</t>
+  </si>
+  <si>
+    <t>Festo QSM Series, 153306 Pneumatic Fitting 6mm Push-in, Male, M5, G</t>
+  </si>
+  <si>
+    <t>0.96 inch oled yellow blue screen</t>
+  </si>
+  <si>
+    <t>254-3586</t>
+  </si>
+  <si>
+    <t>https://uk.rs-online.com/web/p/oled-displays/2543586</t>
+  </si>
+  <si>
+    <t>m3 standoff</t>
+  </si>
+  <si>
+    <t>184-2797</t>
+  </si>
+  <si>
+    <t>Wurth Elektronik M3 Standoff, 10 mm Body, 8 mm Stud, Brass</t>
+  </si>
+  <si>
+    <t>184-2848</t>
+  </si>
+  <si>
+    <t>Wurth Elektronik M3 Standoff, 12 mm Body, 6 mm Stud, Brass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSK-M3-6-A2 </t>
+  </si>
+  <si>
+    <t>m3 countersunk</t>
+  </si>
+  <si>
+    <t>M3 countersunk for battery plate</t>
+  </si>
+  <si>
+    <t>3mm ID 5mm OD PVC tubing</t>
+  </si>
+  <si>
+    <t>218-4297</t>
+  </si>
+  <si>
+    <t>push fit connector</t>
+  </si>
+  <si>
+    <t>289-0796</t>
   </si>
 </sst>
 </file>
@@ -639,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H21"/>
+  <dimension ref="B1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -698,7 +740,7 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
@@ -718,7 +760,7 @@
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
@@ -738,7 +780,7 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
@@ -758,7 +800,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -806,14 +848,17 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
@@ -824,19 +869,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" t="s">
         <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>41</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
@@ -847,17 +892,17 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -868,19 +913,19 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
         <v>32</v>
@@ -891,19 +936,19 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.35">
@@ -911,19 +956,19 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.35">
@@ -931,19 +976,19 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.35">
@@ -951,97 +996,193 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B18" s="5" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
         <v>0</v>
       </c>
-      <c r="C19" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
         <v>2</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E24" t="s">
         <v>3</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F24" t="s">
         <v>4</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G24" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D25" t="s">
         <v>9</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B21">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D26" t="s">
         <v>13</v>
       </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G26" s="6">
         <v>326</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F20" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F21" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F25" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F26" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F10" r:id="rId3" display="https://uk.rs-online.com/web/p/battery-holders/1854647" xr:uid="{9521DDEA-38F0-4C9B-93D2-026EF06185F3}"/>
-    <hyperlink ref="F12" r:id="rId4" display="https://uk.rs-online.com/web/p/oled-displays/2543587" xr:uid="{735C26EA-357D-4045-9841-B353297B07E6}"/>
-    <hyperlink ref="F13" r:id="rId5" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
+    <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF96A9E-FB1A-4F82-90CC-0F46C2486A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FBF96A9E-FB1A-4F82-90CC-0F46C2486A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBF74107-ED26-4888-B02C-80CAE79B615E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
   <si>
     <t>No</t>
   </si>
@@ -267,6 +267,18 @@
   </si>
   <si>
     <t>289-0796</t>
+  </si>
+  <si>
+    <t>m3 brass insert</t>
+  </si>
+  <si>
+    <t>278-534</t>
+  </si>
+  <si>
+    <t>m2 brass insert</t>
+  </si>
+  <si>
+    <t>HTBI-M2-BR</t>
   </si>
 </sst>
 </file>
@@ -681,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H26"/>
+  <dimension ref="B1:H28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -1108,77 +1120,108 @@
         <v>32</v>
       </c>
     </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B23" s="5" t="s">
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
         <v>0</v>
       </c>
-      <c r="C24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>2</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>3</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F26" t="s">
         <v>4</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G26" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>9</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B26">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28">
         <v>2</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" t="s">
         <v>12</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>13</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G28" s="6">
         <v>326</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F25" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F26" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F27" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F28" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F10" r:id="rId3" display="https://uk.rs-online.com/web/p/battery-holders/1854647" xr:uid="{9521DDEA-38F0-4C9B-93D2-026EF06185F3}"/>
     <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
   </hyperlinks>

--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FBF96A9E-FB1A-4F82-90CC-0F46C2486A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBF74107-ED26-4888-B02C-80CAE79B615E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53299886-F7F5-4F11-8640-35745ED59189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
   <si>
     <t>No</t>
   </si>
@@ -248,15 +248,9 @@
     <t>Wurth Elektronik M3 Standoff, 12 mm Body, 6 mm Stud, Brass</t>
   </si>
   <si>
-    <t xml:space="preserve">SSK-M3-6-A2 </t>
-  </si>
-  <si>
     <t>m3 countersunk</t>
   </si>
   <si>
-    <t>M3 countersunk for battery plate</t>
-  </si>
-  <si>
     <t>3mm ID 5mm OD PVC tubing</t>
   </si>
   <si>
@@ -279,6 +273,54 @@
   </si>
   <si>
     <t>HTBI-M2-BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSK-M3-8-A2 </t>
+  </si>
+  <si>
+    <t>M3x8 countersunk</t>
+  </si>
+  <si>
+    <t>Cable gland</t>
+  </si>
+  <si>
+    <t>834-775</t>
+  </si>
+  <si>
+    <t>Rotary encoder</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Temp and humidity sensor</t>
+  </si>
+  <si>
+    <t>https://thepihut.com/products/adafruit-sensirion-sht45-precision-temperature-humidity-sensor-stemma-qt-qwiic?_su_rec=gPgvVkC3dW6FfAEJq0881OPq3ij1vB_9ivObglz7OCtLQ4x9CCdThHfIblPWfjWXhaHp-Zus8pchBDixiEBvxtzl42kSFJXCLvApSIxeqGJQjZOxL-qQVXRPFEycGK4nyFUlvQ9d1l4NTvszKXRB66hcvtZM-w7LyzjejeUuSTZvU1BHrcSJX66WPwzqIMBMte3ImXEEsYUXJIT0WVrBMUbtJprp3CR7IZcgfUrcaSDC2_aDX3a5DxLpMvGPp_IZV6Dtk2z_af85Pg&amp;_su_rec_id=6d4cbdf2-c7e9-45e2-b9f7-1df4307d347d-1792449471&amp;variant=54007545102721</t>
+  </si>
+  <si>
+    <t>PI HUT</t>
+  </si>
+  <si>
+    <t>SSCSOR-M2-8-A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 Sealing </t>
+  </si>
+  <si>
+    <t>M2 Sealing for SHT45 Temp and humidity sensor</t>
+  </si>
+  <si>
+    <t>SHT45</t>
+  </si>
+  <si>
+    <t>M2 Standoff</t>
+  </si>
+  <si>
+    <t>M2 standoff for SHT45 temp and humidity</t>
+  </si>
+  <si>
+    <t>224-0469</t>
   </si>
 </sst>
 </file>
@@ -693,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H28"/>
+  <dimension ref="B1:H34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -863,14 +905,14 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
@@ -1088,16 +1130,16 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>50</v>
@@ -1108,13 +1150,13 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
         <v>32</v>
@@ -1125,10 +1167,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s">
         <v>32</v>
@@ -1139,93 +1181,188 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s">
         <v>50</v>
       </c>
     </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
-        <v>0</v>
+      <c r="B26">
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="E26" t="s">
-        <v>3</v>
-      </c>
       <c r="F26" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" t="s">
-        <v>5</v>
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
         <v>2</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
         <v>12</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D34" t="s">
         <v>13</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G34" s="6">
         <v>326</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F27" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F28" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F33" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F34" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F10" r:id="rId3" display="https://uk.rs-online.com/web/p/battery-holders/1854647" xr:uid="{9521DDEA-38F0-4C9B-93D2-026EF06185F3}"/>
     <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
+    <hyperlink ref="F12" r:id="rId5" xr:uid="{9101D7C0-2B17-464C-B374-CD94E5126C53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53299886-F7F5-4F11-8640-35745ED59189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{53299886-F7F5-4F11-8640-35745ED59189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D62020-0755-4F77-9A81-629E8442C4F8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -302,9 +302,6 @@
     <t>PI HUT</t>
   </si>
   <si>
-    <t>SSCSOR-M2-8-A2</t>
-  </si>
-  <si>
     <t xml:space="preserve">M2 Sealing </t>
   </si>
   <si>
@@ -320,7 +317,10 @@
     <t>M2 standoff for SHT45 temp and humidity</t>
   </si>
   <si>
-    <t>224-0469</t>
+    <t>184-2630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSCSOR-M2-6-A2 </t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1235,7 @@
         <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -1252,16 +1252,16 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s">
         <v>89</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
         <v>50</v>
@@ -1272,16 +1272,16 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
         <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
       </c>
       <c r="E28">
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>

--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{53299886-F7F5-4F11-8640-35745ED59189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D62020-0755-4F77-9A81-629E8442C4F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EC9C7B-35EC-4A62-9C5B-38A8B2C89365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="109">
   <si>
     <t>No</t>
   </si>
@@ -321,6 +321,48 @@
   </si>
   <si>
     <t xml:space="preserve">SSCSOR-M2-6-A2 </t>
+  </si>
+  <si>
+    <t>O Ring</t>
+  </si>
+  <si>
+    <t>772-172</t>
+  </si>
+  <si>
+    <t>RS PRO Silicone O-Ring O-Ring, 130 mm ID, 136 mm OD</t>
+  </si>
+  <si>
+    <t>O ring</t>
+  </si>
+  <si>
+    <t>BS159</t>
+  </si>
+  <si>
+    <t>PolyMax</t>
+  </si>
+  <si>
+    <t>M3 Screw for tank</t>
+  </si>
+  <si>
+    <t>M3 x 20mm Full Thread Socket Cap Head Screws (DIN 912 / ISO 4762) - Stainless Steel (A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSC-M3-20-A2 </t>
+  </si>
+  <si>
+    <t>M3 x 4mm Full Thread Socket Cap Head Screws (DIN 912 / ISO 4762) - Stainless Steel (A2)</t>
+  </si>
+  <si>
+    <t>M2 Screw for SHT45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSCF-M2-4-A2 </t>
+  </si>
+  <si>
+    <t>m2 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPN-M2-A2 </t>
   </si>
 </sst>
 </file>
@@ -735,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H34"/>
+  <dimension ref="B1:H39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -1240,7 +1282,7 @@
       <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H26" t="s">
@@ -1287,82 +1329,174 @@
         <v>32</v>
       </c>
     </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B31" s="5" t="s">
+      <c r="B31">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="G33" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
         <v>0</v>
       </c>
-      <c r="C32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
         <v>2</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E37" t="s">
         <v>3</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F37" t="s">
         <v>4</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>8</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D38" t="s">
         <v>9</v>
       </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B34">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39">
         <v>2</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C39" t="s">
         <v>12</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D39" t="s">
         <v>13</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G39" s="6">
         <v>326</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F33" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F34" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F38" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F39" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F10" r:id="rId3" display="https://uk.rs-online.com/web/p/battery-holders/1854647" xr:uid="{9521DDEA-38F0-4C9B-93D2-026EF06185F3}"/>
     <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
     <hyperlink ref="F12" r:id="rId5" xr:uid="{9101D7C0-2B17-464C-B374-CD94E5126C53}"/>
+    <hyperlink ref="F26" r:id="rId6" display="https://thepihut.com/products/adafruit-sensirion-sht45-precision-temperature-humidity-sensor-stemma-qt-qwiic?_su_rec=gPgvVkC3dW6FfAEJq0881OPq3ij1vB_9ivObglz7OCtLQ4x9CCdThHfIblPWfjWXhaHp-Zus8pchBDixiEBvxtzl42kSFJXCLvApSIxeqGJQjZOxL-qQVXRPFEycGK4nyFUlvQ9d1l4NTvszKXRB66hcvtZM-w7LyzjejeUuSTZvU1BHrcSJX66WPwzqIMBMte3ImXEEsYUXJIT0WVrBMUbtJprp3CR7IZcgfUrcaSDC2_aDX3a5DxLpMvGPp_IZV6Dtk2z_af85Pg&amp;_su_rec_id=6d4cbdf2-c7e9-45e2-b9f7-1df4307d347d-1792449471&amp;variant=54007545102721" xr:uid="{BB88ECE3-8AFC-48BC-9301-E8863F15F13B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EC9C7B-35EC-4A62-9C5B-38A8B2C89365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D163CB-7330-4B31-8D74-8FB67E25B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="115">
   <si>
     <t>No</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t xml:space="preserve">HPN-M2-A2 </t>
+  </si>
+  <si>
+    <t>Pheonix contact 6 way terminal block</t>
+  </si>
+  <si>
+    <t>220-4305</t>
+  </si>
+  <si>
+    <t>Terminal block 6</t>
+  </si>
+  <si>
+    <t>Terminal block 2</t>
+  </si>
+  <si>
+    <t>Pheonix contact 2 way terminal block</t>
+  </si>
+  <si>
+    <t>220-4260</t>
   </si>
 </sst>
 </file>
@@ -777,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H39"/>
+  <dimension ref="B1:H41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -1485,6 +1503,40 @@
       </c>
       <c r="G39" s="6">
         <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D163CB-7330-4B31-8D74-8FB67E25B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E4B410-39FD-48DB-9E53-AFF32235610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
   <si>
     <t>No</t>
   </si>
@@ -381,6 +381,15 @@
   </si>
   <si>
     <t>220-4260</t>
+  </si>
+  <si>
+    <t>RTD Module</t>
+  </si>
+  <si>
+    <t>https://thepihut.com/collections/new-products-maker/products/adafruit-ds3231-precision-rtc-stemma-qt?_su_rec=fWJplwWF6C3IJSyup8joWkrzSEnHXQGQh7Xx6Z8UTCoIXZeAd55wFvCgRr9lB01zDsbbFju39l8itWnOd6yg2FU-ggVe12pEOHP1Uwkw6-XQVqwBIqQ_KIckkRLVf27I1-yW3NMasugoJ88nyQYAFgFl8aWbMSIWdNq8NyZLQvJOiy1216EzqWSn2lz56Sf-XWFSOamgn_iP_9oLw94c9MouHfoGQxOjusUGsCZ7YZjIhQCNnkj7C69Zrkq_QFMHQ8voVprXnHY&amp;_su_rec_id=8916d1a6-0939-43c9-9e52-5482099ece57-1792888263</t>
+  </si>
+  <si>
+    <t>Timer</t>
   </si>
 </sst>
 </file>
@@ -1438,6 +1447,26 @@
         <v>50</v>
       </c>
     </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" t="s">
+        <v>87</v>
+      </c>
+    </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="5" t="s">
         <v>7</v>

--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E4B410-39FD-48DB-9E53-AFF32235610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{78E4B410-39FD-48DB-9E53-AFF32235610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{824A512F-ABA3-46F3-8369-4742F1007183}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -804,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H41"/>
+  <dimension ref="B1:H42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -1467,111 +1467,111 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B36" s="5" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
         <v>0</v>
       </c>
-      <c r="C37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C38" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
         <v>2</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>3</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>4</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G38" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="6">
-        <v>326</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>3</v>
-      </c>
-      <c r="G40" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="6">
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="G41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42">
         <v>4</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>112</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>113</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
         <v>114</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F38" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F39" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F39" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F40" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F10" r:id="rId3" display="https://uk.rs-online.com/web/p/battery-holders/1854647" xr:uid="{9521DDEA-38F0-4C9B-93D2-026EF06185F3}"/>
     <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
     <hyperlink ref="F12" r:id="rId5" xr:uid="{9101D7C0-2B17-464C-B374-CD94E5126C53}"/>

--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/SLSS V6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{78E4B410-39FD-48DB-9E53-AFF32235610D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{824A512F-ABA3-46F3-8369-4742F1007183}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3261F2D7-4FB1-4A88-B754-A08FFCBF19D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="120">
   <si>
     <t>No</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>Timer</t>
+  </si>
+  <si>
+    <t>https://thepihut.com/products/arduino-nano-r4?variant=54562752627073</t>
+  </si>
+  <si>
+    <t>alt duino</t>
   </si>
 </sst>
 </file>
@@ -804,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H42"/>
+  <dimension ref="B1:H43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -1460,7 +1466,7 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H34" t="s">
@@ -1566,6 +1572,14 @@
       </c>
       <c r="G42" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1576,8 +1590,9 @@
     <hyperlink ref="F13" r:id="rId4" display="https://www.amazon.co.uk/Youmile-Adapter-Interface-Conversion-pinheader/dp/B0C6KB34GZ/ref=sr_1_2_sspa?adgrpid=1175378829251379&amp;dib=eyJ2IjoiMSJ9.4G6Ta0nHdTLEh2FocR_6LAopYVw4r2qMzhRCDT8wuntULpYMdpu6Nx0Be-yz8Bj9e9U26IGfEcWXQyRzuzmArJG2SmYsuic1ec-oTgGdOdXSJYU02rsaO30kc5AMmWBO2ToZD0-HwJQ0kFMAQ_JhSWGUdU_aVZCU3bqjRWrfp9hgZlz6zhLWVtaBsl9FhPPzi88WScDckO5v8_0yqNFwJueiIPTQoT8aGONiikb1_Y4.B15R7p4uyFc5DNnBMFue4rskW8Z0N7_tFr-4B-ExBhk&amp;dib_tag=se&amp;gb=2&amp;hvadid=73461375099874&amp;hvbmt=be&amp;hvdev=c&amp;hvexpln=0&amp;hvlocphy=247141&amp;hvnetw=o&amp;hvocijid=15363587760079059900--&amp;hvqmt=e&amp;hvtargid=kwd-73461312780525%3Aloc-188&amp;hydadcr=13504_1855336&amp;keywords=arduino+micro+sd+card+module&amp;mcid=16b5a40d7175347296a474d6f7b883e3&amp;qid=1786454835&amp;sr=8-2-spons&amp;aref=HuQ1cV2wpw&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{89E43225-4AEF-4BE0-8D27-A8DAACFCBDE6}"/>
     <hyperlink ref="F12" r:id="rId5" xr:uid="{9101D7C0-2B17-464C-B374-CD94E5126C53}"/>
     <hyperlink ref="F26" r:id="rId6" display="https://thepihut.com/products/adafruit-sensirion-sht45-precision-temperature-humidity-sensor-stemma-qt-qwiic?_su_rec=gPgvVkC3dW6FfAEJq0881OPq3ij1vB_9ivObglz7OCtLQ4x9CCdThHfIblPWfjWXhaHp-Zus8pchBDixiEBvxtzl42kSFJXCLvApSIxeqGJQjZOxL-qQVXRPFEycGK4nyFUlvQ9d1l4NTvszKXRB66hcvtZM-w7LyzjejeUuSTZvU1BHrcSJX66WPwzqIMBMte3ImXEEsYUXJIT0WVrBMUbtJprp3CR7IZcgfUrcaSDC2_aDX3a5DxLpMvGPp_IZV6Dtk2z_af85Pg&amp;_su_rec_id=6d4cbdf2-c7e9-45e2-b9f7-1df4307d347d-1792449471&amp;variant=54007545102721" xr:uid="{BB88ECE3-8AFC-48BC-9301-E8863F15F13B}"/>
+    <hyperlink ref="F34" r:id="rId7" display="https://thepihut.com/collections/new-products-maker/products/adafruit-ds3231-precision-rtc-stemma-qt?_su_rec=fWJplwWF6C3IJSyup8joWkrzSEnHXQGQh7Xx6Z8UTCoIXZeAd55wFvCgRr9lB01zDsbbFju39l8itWnOd6yg2FU-ggVe12pEOHP1Uwkw6-XQVqwBIqQ_KIckkRLVf27I1-yW3NMasugoJ88nyQYAFgFl8aWbMSIWdNq8NyZLQvJOiy1216EzqWSn2lz56Sf-XWFSOamgn_iP_9oLw94c9MouHfoGQxOjusUGsCZ7YZjIhQCNnkj7C69Zrkq_QFMHQ8voVprXnHY&amp;_su_rec_id=8916d1a6-0939-43c9-9e52-5482099ece57-1792888263" xr:uid="{FE258968-9F7C-492D-B99D-CBCB9FDDDA36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/SLSS V6/SLSS V6 BoM.xlsx
+++ b/SLSS V6/SLSS V6 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\SLSS\SLSS V6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3261F2D7-4FB1-4A88-B754-A08FFCBF19D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD456D2-2074-41B7-B8AD-BC37F9D0444B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="127">
   <si>
     <t>No</t>
   </si>
@@ -146,9 +146,6 @@
     <t>https://uk.rs-online.com/web/p/clip-kits/1440700</t>
   </si>
   <si>
-    <t>Tubing</t>
-  </si>
-  <si>
     <t>Battery holder</t>
   </si>
   <si>
@@ -396,13 +393,37 @@
   </si>
   <si>
     <t>alt duino</t>
+  </si>
+  <si>
+    <t>Tubing FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>MOSFET</t>
+  </si>
+  <si>
+    <t>Infineon HEXFET N-Channel MOSFET, 47 A, 55 V Enhancement, 3-Pin TO-220 IRLZ44NPBF</t>
+  </si>
+  <si>
+    <t>541-0086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPN-M5-A4 </t>
+  </si>
+  <si>
+    <t>M5 Marine</t>
+  </si>
+  <si>
+    <t>M5 Marine nut for water fittings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,6 +451,14 @@
       <color rgb="FF666666"/>
       <name val="Lucida Sans Unicode"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -465,7 +494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -475,6 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -810,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H43"/>
+  <dimension ref="B1:J44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -819,7 +849,7 @@
     <col min="7" max="7" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
@@ -829,7 +859,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -852,7 +882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -869,10 +899,10 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -889,10 +919,10 @@
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -909,10 +939,10 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -929,10 +959,10 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -952,7 +982,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -972,169 +1002,173 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" t="s">
         <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="J10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
         <v>62</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>63</v>
       </c>
       <c r="H12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
         <v>47</v>
       </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
         <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
         <v>49</v>
       </c>
-      <c r="H14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
         <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>57</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -1145,16 +1179,16 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>60</v>
       </c>
       <c r="H17" t="s">
         <v>32</v>
@@ -1165,16 +1199,16 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
         <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>66</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
@@ -1185,16 +1219,16 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
         <v>32</v>
@@ -1205,19 +1239,19 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
@@ -1225,13 +1259,13 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
         <v>73</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>74</v>
       </c>
       <c r="H21" t="s">
         <v>32</v>
@@ -1242,10 +1276,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
         <v>75</v>
-      </c>
-      <c r="G22" t="s">
-        <v>76</v>
       </c>
       <c r="H22" t="s">
         <v>32</v>
@@ -1256,16 +1290,16 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
@@ -1273,13 +1307,13 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
         <v>81</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>82</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
@@ -1290,16 +1324,16 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
         <v>83</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>84</v>
-      </c>
       <c r="H25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
@@ -1307,19 +1341,19 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" t="s">
         <v>86</v>
-      </c>
-      <c r="H26" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
@@ -1327,19 +1361,19 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" t="s">
         <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>89</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
@@ -1347,16 +1381,16 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
         <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>92</v>
       </c>
       <c r="E28">
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
@@ -1367,16 +1401,16 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
         <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>96</v>
       </c>
       <c r="H29" t="s">
         <v>32</v>
@@ -1387,13 +1421,13 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" t="s">
         <v>98</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>99</v>
-      </c>
-      <c r="H30" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
@@ -1401,19 +1435,19 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
         <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.35">
@@ -1421,19 +1455,19 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32">
         <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.35">
@@ -1441,16 +1475,16 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33">
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
@@ -1458,19 +1492,39 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
@@ -1545,16 +1599,16 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
@@ -1562,24 +1616,44 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" t="s">
         <v>112</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
         <v>113</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <v>5</v>
+      </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F43" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
